--- a/out/plan3y/WineBank_3か年計画_FY2027-2029.xlsx
+++ b/out/plan3y/WineBank_3か年計画_FY2027-2029.xlsx
@@ -928,7 +928,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">仲介</t>
+      <t xml:space="preserve">仲介（アピシウス）</t>
     </r>
     <r>
       <rPr>
@@ -945,7 +945,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">百万円は</t>
+      <t xml:space="preserve">百万円は削除。一発だけの案件で、</t>
     </r>
     <r>
       <rPr>
@@ -954,6 +954,23 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に計上済み（戸髙さん版の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">FY2027</t>
     </r>
     <r>
@@ -962,58 +979,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">のみ。★</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に計上済みのアピシウス</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">百万円と同じ案件なら二重計上のため</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">にする（要確認）。</t>
+      <t xml:space="preserve">計上は二重計上）。</t>
     </r>
   </si>
   <si>
@@ -3228,37 +3194,56 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">仲介</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一時収益。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="メイリオ"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF8C8C8C"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以降は案件化が未確定のため</t>
+      <t xml:space="preserve">仲介（アピシウス）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★削除：一発だけの案件で、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">百万円を計上済みのため</t>
     </r>
     <r>
       <rPr>
@@ -3269,6 +3254,34 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（中野確認 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="メイリオ"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
     </r>
   </si>
   <si>
@@ -7408,7 +7421,7 @@
       </c>
       <c r="D6" s="8" t="n">
         <f aca="false">②シナリオ比較!$F$10</f>
-        <v>790173797</v>
+        <v>770173797</v>
       </c>
       <c r="E6" s="8" t="n">
         <f aca="false">②シナリオ比較!$G$10</f>
@@ -7420,7 +7433,7 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">IF(D6&gt;0,(F6/D6)^(1/2)-1,"")</f>
-        <v>0.00630782750535452</v>
+        <v>0.0192900701145797</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>11</v>
@@ -7436,7 +7449,7 @@
       </c>
       <c r="D7" s="8" t="n">
         <f aca="false">②シナリオ比較!$F$11</f>
-        <v>405588700.9</v>
+        <v>385588700.9</v>
       </c>
       <c r="E7" s="8" t="n">
         <f aca="false">②シナリオ比較!$G$11</f>
@@ -7448,7 +7461,7 @@
       </c>
       <c r="G7" s="9" t="n">
         <f aca="false">IF(D7&gt;0,(F7/D7)^(1/2)-1,"")</f>
-        <v>0.0122526953257389</v>
+        <v>0.0381729671458606</v>
       </c>
       <c r="H7" s="2"/>
     </row>
@@ -7462,7 +7475,7 @@
       </c>
       <c r="D8" s="11" t="n">
         <f aca="false">②シナリオ比較!$F$12</f>
-        <v>0.513290496900646</v>
+        <v>0.500651544368238</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">②シナリオ比較!$G$12</f>
@@ -7508,7 +7521,7 @@
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">②シナリオ比較!$F$16</f>
-        <v>83958966.9</v>
+        <v>63958966.9</v>
       </c>
       <c r="E10" s="15" t="n">
         <f aca="false">②シナリオ比較!$G$16</f>
@@ -7520,7 +7533,7 @@
       </c>
       <c r="G10" s="16" t="n">
         <f aca="false">IF(D10&gt;0,(F10/D10)^(1/2)-1,"")</f>
-        <v>0.0304592235305725</v>
+        <v>0.18062950884231</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -7558,7 +7571,7 @@
       </c>
       <c r="D12" s="15" t="n">
         <f aca="false">②シナリオ比較!$F$18</f>
-        <v>71958966.9</v>
+        <v>51958966.9</v>
       </c>
       <c r="E12" s="15" t="n">
         <f aca="false">②シナリオ比較!$G$18</f>
@@ -7570,7 +7583,7 @@
       </c>
       <c r="G12" s="16" t="n">
         <f aca="false">IF(D12&gt;0,(F12/D12)^(1/2)-1,"")</f>
-        <v>0.0619543426893725</v>
+        <v>0.249735341094464</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -7588,7 +7601,7 @@
       </c>
       <c r="F13" s="12" t="n">
         <f aca="false">②シナリオ比較!$H$22</f>
-        <v>17993100.949416</v>
+        <v>11193100.949416</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>21</v>
@@ -7604,7 +7617,7 @@
       </c>
       <c r="D14" s="8" t="n">
         <f aca="false">②シナリオ比較!$F$23</f>
-        <v>71958966.9</v>
+        <v>51958966.9</v>
       </c>
       <c r="E14" s="8" t="n">
         <f aca="false">②シナリオ比較!$G$23</f>
@@ -7612,7 +7625,7 @@
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">②シナリオ比較!$H$23</f>
-        <v>63158409.962984</v>
+        <v>69958409.962984</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="2" t="s">
@@ -7629,11 +7642,11 @@
       </c>
       <c r="D15" s="12" t="n">
         <f aca="false">②シナリオ比較!$F$21</f>
-        <v>110027270.1</v>
+        <v>130027270.1</v>
       </c>
       <c r="E15" s="12" t="n">
         <f aca="false">②シナリオ比較!$G$21</f>
-        <v>28436508.1200001</v>
+        <v>48436508.1200001</v>
       </c>
       <c r="F15" s="12" t="n">
         <f aca="false">②シナリオ比較!$H$21</f>
@@ -7685,7 +7698,7 @@
       </c>
       <c r="D20" s="12" t="n">
         <f aca="false">⑤部門別損益!C10</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
       <c r="E20" s="12" t="n">
         <f aca="false">⑤部門別損益!C28</f>
@@ -7753,7 +7766,7 @@
       </c>
       <c r="D24" s="20" t="n">
         <f aca="false">⑤部門別損益!G10</f>
-        <v>790173797</v>
+        <v>770173797</v>
       </c>
       <c r="E24" s="20" t="n">
         <f aca="false">⑤部門別損益!G28</f>
@@ -7780,7 +7793,7 @@
       </c>
       <c r="D26" s="12" t="n">
         <f aca="false">⑤部門別損益!C14</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
       <c r="E26" s="12" t="n">
         <f aca="false">⑤部門別損益!C32</f>
@@ -7848,7 +7861,7 @@
       </c>
       <c r="D30" s="20" t="n">
         <f aca="false">⑤部門別損益!G14</f>
-        <v>405588700.9</v>
+        <v>385588700.9</v>
       </c>
       <c r="E30" s="20" t="n">
         <f aca="false">⑤部門別損益!G32</f>
@@ -7875,7 +7888,7 @@
       </c>
       <c r="D32" s="12" t="n">
         <f aca="false">⑤部門別損益!C18</f>
-        <v>36759524.5315165</v>
+        <v>16759524.5315165</v>
       </c>
       <c r="E32" s="12" t="n">
         <f aca="false">⑤部門別損益!C36</f>
@@ -7943,7 +7956,7 @@
       </c>
       <c r="D36" s="20" t="n">
         <f aca="false">⑤部門別損益!G18</f>
-        <v>83958966.9</v>
+        <v>63958966.9</v>
       </c>
       <c r="E36" s="20" t="n">
         <f aca="false">⑤部門別損益!G36</f>
@@ -7988,7 +8001,7 @@
       </c>
       <c r="D40" s="12" t="n">
         <f aca="false">②シナリオ比較!$I$10</f>
-        <v>1490173797</v>
+        <v>1470173797</v>
       </c>
       <c r="E40" s="12" t="n">
         <f aca="false">②シナリオ比較!$J$10</f>
@@ -8005,7 +8018,7 @@
       </c>
       <c r="D41" s="12" t="n">
         <f aca="false">②シナリオ比較!$I$18</f>
-        <v>106958966.9</v>
+        <v>86958966.9</v>
       </c>
       <c r="E41" s="12" t="n">
         <f aca="false">②シナリオ比較!$J$18</f>
@@ -8022,15 +8035,15 @@
       </c>
       <c r="D42" s="12" t="n">
         <f aca="false">⑦資金繰り・在庫!C17</f>
-        <v>75398539</v>
+        <v>55398539</v>
       </c>
       <c r="E42" s="12" t="n">
         <f aca="false">⑦資金繰り・在庫!D17</f>
-        <v>130358873.08</v>
+        <v>110358873.08</v>
       </c>
       <c r="F42" s="12" t="n">
         <f aca="false">⑦資金繰り・在庫!E17</f>
-        <v>166956855.142984</v>
+        <v>153756855.142984</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8039,15 +8052,15 @@
       </c>
       <c r="D43" s="12" t="n">
         <f aca="false">⑦資金繰り・在庫!F17</f>
-        <v>110398539</v>
+        <v>90398539</v>
       </c>
       <c r="E43" s="12" t="n">
         <f aca="false">⑦資金繰り・在庫!G17</f>
-        <v>196127285.8408</v>
+        <v>182927285.8408</v>
       </c>
       <c r="F43" s="12" t="n">
         <f aca="false">⑦資金繰り・在庫!H17</f>
-        <v>256056855.142984</v>
+        <v>242856855.142984</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8642,7 +8655,7 @@
         <v>99</v>
       </c>
       <c r="D39" s="22" t="n">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="E39" s="22" t="n">
         <v>0</v>
@@ -8654,7 +8667,7 @@
         <v>94</v>
       </c>
       <c r="H39" s="29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I39" s="13" t="s">
         <v>100</v>
@@ -8689,7 +8702,7 @@
       </c>
       <c r="D41" s="15" t="n">
         <f aca="false">SUM(D36:D40)</f>
-        <v>132500000</v>
+        <v>112500000</v>
       </c>
       <c r="E41" s="15" t="n">
         <f aca="false">SUM(E36:E40)</f>
@@ -9701,7 +9714,7 @@
       </c>
       <c r="F9" s="12" t="n">
         <f aca="false">③前提!$D$41</f>
-        <v>132500000</v>
+        <v>112500000</v>
       </c>
       <c r="G9" s="12" t="n">
         <f aca="false">③前提!$E$41</f>
@@ -9713,7 +9726,7 @@
       </c>
       <c r="I9" s="12" t="n">
         <f aca="false">③前提!$D$41</f>
-        <v>132500000</v>
+        <v>112500000</v>
       </c>
       <c r="J9" s="12" t="n">
         <f aca="false">③前提!$E$41</f>
@@ -9742,7 +9755,7 @@
       </c>
       <c r="F10" s="8" t="n">
         <f aca="false">F6+F8+F9</f>
-        <v>790173797</v>
+        <v>770173797</v>
       </c>
       <c r="G10" s="8" t="n">
         <f aca="false">G6+G8+G9</f>
@@ -9754,7 +9767,7 @@
       </c>
       <c r="I10" s="8" t="n">
         <f aca="false">I6+I8+I9</f>
-        <v>1490173797</v>
+        <v>1470173797</v>
       </c>
       <c r="J10" s="8" t="n">
         <f aca="false">J6+J8+J9</f>
@@ -9783,7 +9796,7 @@
       </c>
       <c r="F11" s="8" t="n">
         <f aca="false">③前提!$C$22+F7*③前提!$C$32+F8*③前提!$D$46+F9</f>
-        <v>405588700.9</v>
+        <v>385588700.9</v>
       </c>
       <c r="G11" s="8" t="n">
         <f aca="false">③前提!$C$22+G7*③前提!$C$32+G8*③前提!$E$46+G9</f>
@@ -9795,7 +9808,7 @@
       </c>
       <c r="I11" s="8" t="n">
         <f aca="false">③前提!$C$22+I7*③前提!$C$32+I8*③前提!$D$46+I9</f>
-        <v>440588700.9</v>
+        <v>420588700.9</v>
       </c>
       <c r="J11" s="8" t="n">
         <f aca="false">③前提!$C$22+J7*③前提!$C$32+J8*③前提!$E$46+J9</f>
@@ -9824,7 +9837,7 @@
       </c>
       <c r="F12" s="11" t="n">
         <f aca="false">F11/F10</f>
-        <v>0.513290496900646</v>
+        <v>0.500651544368238</v>
       </c>
       <c r="G12" s="11" t="n">
         <f aca="false">G11/G10</f>
@@ -9836,7 +9849,7 @@
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">I11/I10</f>
-        <v>0.295662627934398</v>
+        <v>0.286080939381618</v>
       </c>
       <c r="J12" s="11" t="n">
         <f aca="false">J11/J10</f>
@@ -9988,7 +10001,7 @@
       </c>
       <c r="F16" s="15" t="n">
         <f aca="false">F11-F15</f>
-        <v>83958966.9</v>
+        <v>63958966.9</v>
       </c>
       <c r="G16" s="15" t="n">
         <f aca="false">G11-G15</f>
@@ -10000,7 +10013,7 @@
       </c>
       <c r="I16" s="15" t="n">
         <f aca="false">I11-I15</f>
-        <v>118958966.9</v>
+        <v>98958966.9</v>
       </c>
       <c r="J16" s="15" t="n">
         <f aca="false">J11-J15</f>
@@ -10070,7 +10083,7 @@
       </c>
       <c r="F18" s="15" t="n">
         <f aca="false">F16-F17</f>
-        <v>71958966.9</v>
+        <v>51958966.9</v>
       </c>
       <c r="G18" s="15" t="n">
         <f aca="false">G16-G17</f>
@@ -10082,7 +10095,7 @@
       </c>
       <c r="I18" s="15" t="n">
         <f aca="false">I16-I17</f>
-        <v>106958966.9</v>
+        <v>86958966.9</v>
       </c>
       <c r="J18" s="15" t="n">
         <f aca="false">J16-J17</f>
@@ -10115,11 +10128,11 @@
       </c>
       <c r="G19" s="12" t="n">
         <f aca="false">F21</f>
-        <v>110027270.1</v>
+        <v>130027270.1</v>
       </c>
       <c r="H19" s="12" t="n">
         <f aca="false">G21</f>
-        <v>28436508.1200001</v>
+        <v>48436508.1200001</v>
       </c>
       <c r="I19" s="12" t="n">
         <f aca="false">④FY2026着地!$H$19</f>
@@ -10127,7 +10140,7 @@
       </c>
       <c r="J19" s="12" t="n">
         <f aca="false">I21</f>
-        <v>75027270.1</v>
+        <v>95027270.1</v>
       </c>
       <c r="K19" s="12" t="n">
         <f aca="false">J21</f>
@@ -10152,7 +10165,7 @@
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">MIN(F19,MAX(0,F18))</f>
-        <v>71958966.9</v>
+        <v>51958966.9</v>
       </c>
       <c r="G20" s="12" t="n">
         <f aca="false">MIN(G19,MAX(0,G18))</f>
@@ -10160,15 +10173,15 @@
       </c>
       <c r="H20" s="12" t="n">
         <f aca="false">MIN(H19,MAX(0,H18))</f>
-        <v>28436508.1200001</v>
+        <v>48436508.1200001</v>
       </c>
       <c r="I20" s="12" t="n">
         <f aca="false">MIN(I19,MAX(0,I18))</f>
-        <v>106958966.9</v>
+        <v>86958966.9</v>
       </c>
       <c r="J20" s="12" t="n">
         <f aca="false">MIN(J19,MAX(0,J18))</f>
-        <v>75027270.1</v>
+        <v>95027270.1</v>
       </c>
       <c r="K20" s="12" t="n">
         <f aca="false">MIN(K19,MAX(0,K18))</f>
@@ -10193,11 +10206,11 @@
       </c>
       <c r="F21" s="12" t="n">
         <f aca="false">F19-F20+MAX(0,-F18)</f>
-        <v>110027270.1</v>
+        <v>130027270.1</v>
       </c>
       <c r="G21" s="12" t="n">
         <f aca="false">G19-G20+MAX(0,-G18)</f>
-        <v>28436508.1200001</v>
+        <v>48436508.1200001</v>
       </c>
       <c r="H21" s="12" t="n">
         <f aca="false">H19-H20+MAX(0,-H18)</f>
@@ -10205,7 +10218,7 @@
       </c>
       <c r="I21" s="12" t="n">
         <f aca="false">I19-I20+MAX(0,-I18)</f>
-        <v>75027270.1</v>
+        <v>95027270.1</v>
       </c>
       <c r="J21" s="12" t="n">
         <f aca="false">J19-J20+MAX(0,-J18)</f>
@@ -10242,7 +10255,7 @@
       </c>
       <c r="H22" s="12" t="n">
         <f aca="false">MAX(0,H18-H20)*③前提!$F$53+③前提!$F$54</f>
-        <v>17993100.949416</v>
+        <v>11193100.949416</v>
       </c>
       <c r="I22" s="12" t="n">
         <f aca="false">MAX(0,I18-I20)*③前提!$D$53+③前提!$D$54</f>
@@ -10250,7 +10263,7 @@
       </c>
       <c r="J22" s="12" t="n">
         <f aca="false">MAX(0,J18-J20)*③前提!$E$53+③前提!$E$54</f>
-        <v>19301587.2392</v>
+        <v>12501587.2392</v>
       </c>
       <c r="K22" s="12" t="n">
         <f aca="false">MAX(0,K18-K20)*③前提!$F$53+③前提!$F$54</f>
@@ -10275,7 +10288,7 @@
       </c>
       <c r="F23" s="8" t="n">
         <f aca="false">F18-F22</f>
-        <v>71958966.9</v>
+        <v>51958966.9</v>
       </c>
       <c r="G23" s="8" t="n">
         <f aca="false">G18-G22</f>
@@ -10283,15 +10296,15 @@
       </c>
       <c r="H23" s="8" t="n">
         <f aca="false">H18-H22</f>
-        <v>63158409.962984</v>
+        <v>69958409.962984</v>
       </c>
       <c r="I23" s="8" t="n">
         <f aca="false">I18-I22</f>
-        <v>106958966.9</v>
+        <v>86958966.9</v>
       </c>
       <c r="J23" s="8" t="n">
         <f aca="false">J18-J22</f>
-        <v>112289174.7408</v>
+        <v>119089174.7408</v>
       </c>
       <c r="K23" s="8" t="n">
         <f aca="false">K18-K22</f>
@@ -10485,7 +10498,7 @@
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">SUMIF(③前提!$G$36:$G$40,"本部",③前提!D$36:D$40)</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
       <c r="D9" s="12" t="n">
         <f aca="false">SUMIF(③前提!$G$36:$G$40,"EC/酒販店卸",③前提!D$36:D$40)</f>
@@ -10501,7 +10514,7 @@
       </c>
       <c r="G9" s="8" t="n">
         <f aca="false">SUM(C9:F9)</f>
-        <v>132500000</v>
+        <v>112500000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10510,7 +10523,7 @@
       </c>
       <c r="C10" s="8" t="n">
         <f aca="false">SUM(C7:C9)</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
       <c r="D10" s="8" t="n">
         <f aca="false">SUM(D7:D9)</f>
@@ -10526,7 +10539,7 @@
       </c>
       <c r="G10" s="8" t="n">
         <f aca="false">SUM(C10:F10)</f>
-        <v>790173797</v>
+        <v>770173797</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10585,7 +10598,7 @@
       </c>
       <c r="C13" s="12" t="n">
         <f aca="false">C9</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
       <c r="D13" s="12" t="n">
         <f aca="false">D9</f>
@@ -10601,7 +10614,7 @@
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">SUM(C13:F13)</f>
-        <v>132500000</v>
+        <v>112500000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10610,7 +10623,7 @@
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">SUM(C11:C13)</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
       <c r="D14" s="8" t="n">
         <f aca="false">SUM(D11:D13)</f>
@@ -10626,7 +10639,7 @@
       </c>
       <c r="G14" s="8" t="n">
         <f aca="false">SUM(C14:F14)</f>
-        <v>405588700.9</v>
+        <v>385588700.9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10710,7 +10723,7 @@
       </c>
       <c r="C18" s="15" t="n">
         <f aca="false">C14-C17</f>
-        <v>36759524.5315165</v>
+        <v>16759524.5315165</v>
       </c>
       <c r="D18" s="15" t="n">
         <f aca="false">D14-D17</f>
@@ -10726,7 +10739,7 @@
       </c>
       <c r="G18" s="8" t="n">
         <f aca="false">SUM(C18:F18)</f>
-        <v>83958966.9</v>
+        <v>63958966.9</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10760,7 +10773,7 @@
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">C18+C19</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
       <c r="D20" s="15" t="n">
         <f aca="false">D18+D19</f>
@@ -10776,7 +10789,7 @@
       </c>
       <c r="G20" s="8" t="n">
         <f aca="false">SUM(C20:F20)</f>
-        <v>83958966.9</v>
+        <v>63958966.9</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11698,7 +11711,7 @@
       </c>
       <c r="H7" s="12" t="n">
         <f aca="false">(⑤部門別損益!C7+⑤部門別損益!C8)/12+IF(③前提!$G$36="本部",IF(③前提!$H$36=0,③前提!$D$36/12,IF(③前提!$H$36=6,③前提!$D$36,0)),0)+IF(③前提!$G$37="本部",IF(③前提!$H$37=0,③前提!$D$37/12,IF(③前提!$H$37=6,③前提!$D$37,0)),0)+IF(③前提!$G$38="本部",IF(③前提!$H$38=0,③前提!$D$38/12,IF(③前提!$H$38=6,③前提!$D$38,0)),0)+IF(③前提!$G$39="本部",IF(③前提!$H$39=0,③前提!$D$39/12,IF(③前提!$H$39=6,③前提!$D$39,0)),0)+IF(③前提!$G$40="本部",IF(③前提!$H$40=0,③前提!$D$40/12,IF(③前提!$H$40=6,③前提!$D$40,0)),0)</f>
-        <v>27708333.3333333</v>
+        <v>7708333.33333333</v>
       </c>
       <c r="I7" s="12" t="n">
         <f aca="false">(⑤部門別損益!C7+⑤部門別損益!C8)/12+IF(③前提!$G$36="本部",IF(③前提!$H$36=0,③前提!$D$36/12,IF(③前提!$H$36=7,③前提!$D$36,0)),0)+IF(③前提!$G$37="本部",IF(③前提!$H$37=0,③前提!$D$37/12,IF(③前提!$H$37=7,③前提!$D$37,0)),0)+IF(③前提!$G$38="本部",IF(③前提!$H$38=0,③前提!$D$38/12,IF(③前提!$H$38=7,③前提!$D$38,0)),0)+IF(③前提!$G$39="本部",IF(③前提!$H$39=0,③前提!$D$39/12,IF(③前提!$H$39=7,③前提!$D$39,0)),0)+IF(③前提!$G$40="本部",IF(③前提!$H$40=0,③前提!$D$40/12,IF(③前提!$H$40=7,③前提!$D$40,0)),0)</f>
@@ -11726,7 +11739,7 @@
       </c>
       <c r="O7" s="8" t="n">
         <f aca="false">SUM(C7:N7)</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11755,7 +11768,7 @@
       </c>
       <c r="H8" s="12" t="n">
         <f aca="false">(⑤部門別損益!C11+⑤部門別損益!C12)/12+IF(③前提!$G$36="本部",IF(③前提!$H$36=0,③前提!$D$36/12,IF(③前提!$H$36=6,③前提!$D$36,0)),0)+IF(③前提!$G$37="本部",IF(③前提!$H$37=0,③前提!$D$37/12,IF(③前提!$H$37=6,③前提!$D$37,0)),0)+IF(③前提!$G$38="本部",IF(③前提!$H$38=0,③前提!$D$38/12,IF(③前提!$H$38=6,③前提!$D$38,0)),0)+IF(③前提!$G$39="本部",IF(③前提!$H$39=0,③前提!$D$39/12,IF(③前提!$H$39=6,③前提!$D$39,0)),0)+IF(③前提!$G$40="本部",IF(③前提!$H$40=0,③前提!$D$40/12,IF(③前提!$H$40=6,③前提!$D$40,0)),0)</f>
-        <v>27708333.3333333</v>
+        <v>7708333.33333333</v>
       </c>
       <c r="I8" s="12" t="n">
         <f aca="false">(⑤部門別損益!C11+⑤部門別損益!C12)/12+IF(③前提!$G$36="本部",IF(③前提!$H$36=0,③前提!$D$36/12,IF(③前提!$H$36=7,③前提!$D$36,0)),0)+IF(③前提!$G$37="本部",IF(③前提!$H$37=0,③前提!$D$37/12,IF(③前提!$H$37=7,③前提!$D$37,0)),0)+IF(③前提!$G$38="本部",IF(③前提!$H$38=0,③前提!$D$38/12,IF(③前提!$H$38=7,③前提!$D$38,0)),0)+IF(③前提!$G$39="本部",IF(③前提!$H$39=0,③前提!$D$39/12,IF(③前提!$H$39=7,③前提!$D$39,0)),0)+IF(③前提!$G$40="本部",IF(③前提!$H$40=0,③前提!$D$40/12,IF(③前提!$H$40=7,③前提!$D$40,0)),0)</f>
@@ -11783,7 +11796,7 @@
       </c>
       <c r="O8" s="8" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>112500000</v>
+        <v>92500000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11869,7 +11882,7 @@
       </c>
       <c r="H10" s="15" t="n">
         <f aca="false">H8-H9</f>
-        <v>21396627.044293</v>
+        <v>1396627.04429304</v>
       </c>
       <c r="I10" s="15" t="n">
         <f aca="false">I8-I9</f>
@@ -11897,7 +11910,7 @@
       </c>
       <c r="O10" s="8" t="n">
         <f aca="false">SUM(C10:N10)</f>
-        <v>36759524.5315165</v>
+        <v>16759524.5315165</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12858,7 +12871,7 @@
       </c>
       <c r="H35" s="12" t="n">
         <f aca="false">H7+H14+H21+H28</f>
-        <v>84181149.75</v>
+        <v>64181149.75</v>
       </c>
       <c r="I35" s="12" t="n">
         <f aca="false">I7+I14+I21+I28</f>
@@ -12886,7 +12899,7 @@
       </c>
       <c r="O35" s="8" t="n">
         <f aca="false">SUM(C35:N35)</f>
-        <v>790173797</v>
+        <v>770173797</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12915,7 +12928,7 @@
       </c>
       <c r="H36" s="12" t="n">
         <f aca="false">H8+H15+H22+H29</f>
-        <v>52132391.7416667</v>
+        <v>32132391.7416667</v>
       </c>
       <c r="I36" s="12" t="n">
         <f aca="false">I8+I15+I22+I29</f>
@@ -12943,7 +12956,7 @@
       </c>
       <c r="O36" s="8" t="n">
         <f aca="false">SUM(C36:N36)</f>
-        <v>405588700.9</v>
+        <v>385588700.9</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13029,7 +13042,7 @@
       </c>
       <c r="H38" s="15" t="n">
         <f aca="false">H10+H17+H24+H31</f>
-        <v>25329913.9083333</v>
+        <v>5329913.90833333</v>
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">I10+I17+I24+I31</f>
@@ -13057,7 +13070,7 @@
       </c>
       <c r="O38" s="8" t="n">
         <f aca="false">SUM(C38:N38)</f>
-        <v>83958966.9</v>
+        <v>63958966.9</v>
       </c>
     </row>
   </sheetData>
@@ -13253,11 +13266,11 @@
       </c>
       <c r="D11" s="12" t="n">
         <f aca="false">C17</f>
-        <v>75398539</v>
+        <v>55398539</v>
       </c>
       <c r="E11" s="12" t="n">
         <f aca="false">D17</f>
-        <v>130358873.08</v>
+        <v>110358873.08</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">③前提!$C$58</f>
@@ -13265,11 +13278,11 @@
       </c>
       <c r="G11" s="12" t="n">
         <f aca="false">F17</f>
-        <v>110398539</v>
+        <v>90398539</v>
       </c>
       <c r="H11" s="12" t="n">
         <f aca="false">G17</f>
-        <v>196127285.8408</v>
+        <v>182927285.8408</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13278,7 +13291,7 @@
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">②シナリオ比較!$F$18</f>
-        <v>71958966.9</v>
+        <v>51958966.9</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">②シナリオ比較!$G$18</f>
@@ -13290,7 +13303,7 @@
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">②シナリオ比較!$I$18</f>
-        <v>106958966.9</v>
+        <v>86958966.9</v>
       </c>
       <c r="G12" s="12" t="n">
         <f aca="false">②シナリオ比較!$J$18</f>
@@ -13344,7 +13357,7 @@
       </c>
       <c r="E14" s="12" t="n">
         <f aca="false">-②シナリオ比較!$H$22</f>
-        <v>-17993100.949416</v>
+        <v>-11193100.949416</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">-②シナリオ比較!$I$22</f>
@@ -13352,7 +13365,7 @@
       </c>
       <c r="G14" s="12" t="n">
         <f aca="false">-②シナリオ比較!$J$22</f>
-        <v>-19301587.2392</v>
+        <v>-12501587.2392</v>
       </c>
       <c r="H14" s="12" t="n">
         <f aca="false">-②シナリオ比較!$K$22</f>
@@ -13423,27 +13436,27 @@
       </c>
       <c r="C17" s="15" t="n">
         <f aca="false">SUM(C11:C16)</f>
-        <v>75398539</v>
+        <v>55398539</v>
       </c>
       <c r="D17" s="15" t="n">
         <f aca="false">SUM(D11:D16)</f>
-        <v>130358873.08</v>
+        <v>110358873.08</v>
       </c>
       <c r="E17" s="15" t="n">
         <f aca="false">SUM(E11:E16)</f>
-        <v>166956855.142984</v>
+        <v>153756855.142984</v>
       </c>
       <c r="F17" s="15" t="n">
         <f aca="false">SUM(F11:F16)</f>
-        <v>110398539</v>
+        <v>90398539</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">SUM(G11:G16)</f>
-        <v>196127285.8408</v>
+        <v>182927285.8408</v>
       </c>
       <c r="H17" s="15" t="n">
         <f aca="false">SUM(H11:H16)</f>
-        <v>256056855.142984</v>
+        <v>242856855.142984</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
